--- a/dati/esportazioni.xlsx
+++ b/dati/esportazioni.xlsx
@@ -160,13 +160,13 @@
     <t>€ 2.069,75</t>
   </si>
   <si>
-    <t>€ 32.064,77</t>
+    <t>€ 49.332,02</t>
   </si>
   <si>
     <t>€ 644,87</t>
   </si>
   <si>
-    <t>€ 6.848,94</t>
+    <t>€ 7.884,74</t>
   </si>
   <si>
     <t>€ 15.419,72</t>
@@ -184,13 +184,13 @@
     <t>€ 428,19</t>
   </si>
   <si>
-    <t>€ 3.173,91</t>
-  </si>
-  <si>
-    <t>€ 1.750,96</t>
-  </si>
-  <si>
-    <t>€ 577,50</t>
+    <t>€ 3.660,00</t>
+  </si>
+  <si>
+    <t>€ 2.023,33</t>
+  </si>
+  <si>
+    <t>€ 665,95</t>
   </si>
   <si>
     <t>€ 4.116,94</t>
@@ -199,19 +199,19 @@
     <t>€ 9.190,68</t>
   </si>
   <si>
-    <t>€ 8.399,49</t>
+    <t>€ 12.922,30</t>
   </si>
   <si>
     <t>€ 7.298,42</t>
   </si>
   <si>
-    <t>€ 18.949,54</t>
+    <t>€ 21.864,85</t>
   </si>
   <si>
     <t>€ 8.526,54</t>
   </si>
   <si>
-    <t>€ 2.208,62</t>
+    <t>€ 3.408,96</t>
   </si>
   <si>
     <t>€ 6.556,66</t>
@@ -238,7 +238,7 @@
     <t>€ -63,07</t>
   </si>
   <si>
-    <t>€ 3.666,13</t>
+    <t>€ 5.643,79</t>
   </si>
   <si>
     <t>€ 3.441,95</t>
@@ -280,13 +280,13 @@
     <t>€ 17.561,32</t>
   </si>
   <si>
-    <t>€ 476,83</t>
+    <t>€ 733,45</t>
   </si>
   <si>
     <t>€ 169,62</t>
   </si>
   <si>
-    <t>€ 2.129,70</t>
+    <t>€ 3.276,61</t>
   </si>
   <si>
     <t>-</t>
@@ -304,7 +304,7 @@
     <t>€ 16.083,69</t>
   </si>
   <si>
-    <t>€ 10.439,09</t>
+    <t>€ 16.051,61</t>
   </si>
   <si>
     <t>€ 3.807,18</t>
@@ -340,7 +340,7 @@
     <t>€ 5.303,12</t>
   </si>
   <si>
-    <t>€ 382,72</t>
+    <t>€ 440,12</t>
   </si>
   <si>
     <t>€ 362,46</t>
@@ -361,10 +361,10 @@
     <t>€ 23.636,19</t>
   </si>
   <si>
-    <t>€ 2.078,63</t>
-  </si>
-  <si>
-    <t>€ 3.008,46</t>
+    <t>€ 2.397,84</t>
+  </si>
+  <si>
+    <t>€ 3.489,81</t>
   </si>
   <si>
     <t>€ 11.857,39</t>
@@ -385,7 +385,7 @@
     <t>€ 681,78</t>
   </si>
   <si>
-    <t>€ 5.968,04</t>
+    <t>€ 6.884,02</t>
   </si>
   <si>
     <t>€ 6.425,40</t>
@@ -415,7 +415,7 @@
     <t>€ 3.411,76</t>
   </si>
   <si>
-    <t>€ 7.002,66</t>
+    <t>€ 8.094,25</t>
   </si>
   <si>
     <t>€ 7.779,38</t>
@@ -481,10 +481,10 @@
     <t>€ 12.675,56</t>
   </si>
   <si>
-    <t>€ 5.242,51</t>
-  </si>
-  <si>
-    <t>€ 598,46</t>
+    <t>€ 8.062,19</t>
+  </si>
+  <si>
+    <t>€ 690,93</t>
   </si>
   <si>
     <t>€ 3.564,06</t>
@@ -493,7 +493,7 @@
     <t>€ 6.221,78</t>
   </si>
   <si>
-    <t>€ 602,08</t>
+    <t>€ 694,89</t>
   </si>
   <si>
     <t>€ 4.360,36</t>
@@ -523,10 +523,10 @@
     <t>€ 528,30</t>
   </si>
   <si>
-    <t>€ 6.938,01</t>
-  </si>
-  <si>
-    <t>€ 2.316,82</t>
+    <t>€ 8.013,51</t>
+  </si>
+  <si>
+    <t>€ 3.565,62</t>
   </si>
   <si>
     <t>€ 4.060,68</t>
@@ -535,10 +535,10 @@
     <t>€ 2.787,16</t>
   </si>
   <si>
-    <t>€ 729,57</t>
-  </si>
-  <si>
-    <t>€ 20.061,57</t>
+    <t>€ 841,96</t>
+  </si>
+  <si>
+    <t>€ 30.873,44</t>
   </si>
   <si>
     <t>€ 4.184,39</t>
@@ -580,16 +580,16 @@
     <t>€ 6.278,79</t>
   </si>
   <si>
-    <t>€ 1.070,65</t>
+    <t>€ 1.236,50</t>
   </si>
   <si>
     <t>€ 3.378,40</t>
   </si>
   <si>
-    <t>€ 5.239,26</t>
-  </si>
-  <si>
-    <t>€ 3.041,73</t>
+    <t>€ 6.047,66</t>
+  </si>
+  <si>
+    <t>€ 3.518,27</t>
   </si>
   <si>
     <t>€ 772,66</t>
@@ -598,10 +598,10 @@
     <t>€ 1.653,13</t>
   </si>
   <si>
-    <t>€ 2.468,90</t>
-  </si>
-  <si>
-    <t>€ 839,58</t>
+    <t>€ 3.799,65</t>
+  </si>
+  <si>
+    <t>€ 1.293,62</t>
   </si>
   <si>
     <t>€ 893,72</t>
@@ -610,13 +610,13 @@
     <t>€ 801,07</t>
   </si>
   <si>
-    <t>€ 5.783,02</t>
-  </si>
-  <si>
-    <t>€ 10.304,03</t>
-  </si>
-  <si>
-    <t>€ 1.010,01</t>
+    <t>€ 8.905,02</t>
+  </si>
+  <si>
+    <t>€ 15.853,96</t>
+  </si>
+  <si>
+    <t>€ 1.164,83</t>
   </si>
   <si>
     <t>€ 1.671,56</t>
@@ -640,7 +640,7 @@
     <t>€ 9.145,40</t>
   </si>
   <si>
-    <t>€ 4.459,26</t>
+    <t>€ 6.863,01</t>
   </si>
   <si>
     <t>€ 1.674,92</t>
@@ -655,7 +655,7 @@
     <t>€ 377,52</t>
   </si>
   <si>
-    <t>€ 6.023,26</t>
+    <t>€ 6.949,92</t>
   </si>
   <si>
     <t>€ 838,87</t>
@@ -688,7 +688,7 @@
     <t>€ 955,76</t>
   </si>
   <si>
-    <t>€ -107,36</t>
+    <t>€ -163,87</t>
   </si>
   <si>
     <t>€ 867,73</t>
@@ -703,7 +703,7 @@
     <t>€ 741,29</t>
   </si>
   <si>
-    <t>€ 1.989,33</t>
+    <t>€ 3.059,40</t>
   </si>
   <si>
     <t>€ 1.053,59</t>
@@ -742,7 +742,7 @@
     <t>€ 1.215,02</t>
   </si>
   <si>
-    <t>€ 3.685,33</t>
+    <t>€ 4.256,03</t>
   </si>
   <si>
     <t>€ 1.491,99</t>
@@ -775,16 +775,16 @@
     <t>€ 2.747,62</t>
   </si>
   <si>
-    <t>€ 702,22</t>
+    <t>€ 1.078,84</t>
   </si>
   <si>
     <t>€ 4.166,00</t>
   </si>
   <si>
-    <t>€ 41.237,98</t>
-  </si>
-  <si>
-    <t>€ 3.085,43</t>
+    <t>€ 63.444,63</t>
+  </si>
+  <si>
+    <t>€ 4.751,02</t>
   </si>
   <si>
     <t>€ 1.044,32</t>
@@ -808,7 +808,7 @@
     <t>€ 4.268,43</t>
   </si>
   <si>
-    <t>€ 13.012,95</t>
+    <t>€ 20.013,45</t>
   </si>
   <si>
     <t>€ 1.503,04</t>
@@ -841,7 +841,7 @@
     <t>€ 9.143,11</t>
   </si>
   <si>
-    <t>€ -56,83</t>
+    <t>€ -65,19</t>
   </si>
   <si>
     <t>€ 3.147,89</t>
@@ -892,7 +892,7 @@
     <t>€ 1.310,19</t>
   </si>
   <si>
-    <t>€ 2.539,68</t>
+    <t>€ 3.907,95</t>
   </si>
   <si>
     <t>€ 8.405,66</t>
@@ -910,7 +910,7 @@
     <t>€ 7.069,08</t>
   </si>
   <si>
-    <t>€ 1.200,50</t>
+    <t>€ 1.384,66</t>
   </si>
   <si>
     <t>€ 7.140,17</t>
@@ -931,7 +931,7 @@
     <t>€ 4.714,86</t>
   </si>
   <si>
-    <t>€ 365,12</t>
+    <t>€ 559,54</t>
   </si>
   <si>
     <t>€ 425,61</t>
@@ -946,7 +946,7 @@
     <t>€ -36,15</t>
   </si>
   <si>
-    <t>€ 2.075,80</t>
+    <t>€ 2.401,59</t>
   </si>
   <si>
     <t>€ 2.383,59</t>
@@ -955,7 +955,7 @@
     <t>€ 3.760,89</t>
   </si>
   <si>
-    <t>€ 16.490,86</t>
+    <t>€ 25.380,30</t>
   </si>
   <si>
     <t>€ 394,57</t>
@@ -964,7 +964,7 @@
     <t>€ 6.561,50</t>
   </si>
   <si>
-    <t>€ 629,76</t>
+    <t>€ 727,22</t>
   </si>
   <si>
     <t>€ 13.471,81</t>
@@ -976,13 +976,13 @@
     <t>€ 683,86</t>
   </si>
   <si>
-    <t>€ 15.178,79</t>
-  </si>
-  <si>
-    <t>€ 852,14</t>
-  </si>
-  <si>
-    <t>€ 8.142,12</t>
+    <t>€ 23.351,98</t>
+  </si>
+  <si>
+    <t>€ 983,82</t>
+  </si>
+  <si>
+    <t>€ 12.515,12</t>
   </si>
   <si>
     <t>€ 1.538,70</t>
@@ -991,7 +991,7 @@
     <t>€ 3.207,71</t>
   </si>
   <si>
-    <t>€ 17.989,77</t>
+    <t>€ 20.758,94</t>
   </si>
   <si>
     <t>€ 8.275,15</t>
@@ -1021,7 +1021,7 @@
     <t>€ 1.283,71</t>
   </si>
   <si>
-    <t>€ 16.389,34</t>
+    <t>€ 18.909,15</t>
   </si>
   <si>
     <t>€ 7.194,95</t>
@@ -1036,7 +1036,7 @@
     <t>€ 1.014,60</t>
   </si>
   <si>
-    <t>€ 1.626,34</t>
+    <t>€ 1.876,54</t>
   </si>
   <si>
     <t>€ 1.026,47</t>
@@ -1063,16 +1063,16 @@
     <t>€ 2.885,89</t>
   </si>
   <si>
-    <t>€ 1.461,23</t>
+    <t>€ 1.687,15</t>
   </si>
   <si>
     <t>€ 341,29</t>
   </si>
   <si>
-    <t>€ 11.731,37</t>
-  </si>
-  <si>
-    <t>€ 917,04</t>
+    <t>€ 13.539,42</t>
+  </si>
+  <si>
+    <t>€ 1.058,27</t>
   </si>
   <si>
     <t>€ -2.832,48</t>
@@ -1099,10 +1099,10 @@
     <t>€ 23.462,10</t>
   </si>
   <si>
-    <t>€ 2.167,19</t>
-  </si>
-  <si>
-    <t>€ 17.549,07</t>
+    <t>€ 3.336,37</t>
+  </si>
+  <si>
+    <t>€ 20.248,92</t>
   </si>
   <si>
     <t>€ 8.649,73</t>
@@ -1126,7 +1126,7 @@
     <t>€ 3.455,82</t>
   </si>
   <si>
-    <t>€ 6.142,66</t>
+    <t>€ 7.086,95</t>
   </si>
   <si>
     <t>€ 1.189,65</t>
@@ -1204,7 +1204,7 @@
     <t>€ 9.744,72</t>
   </si>
   <si>
-    <t>€ 3.069,49</t>
+    <t>€ 3.546,50</t>
   </si>
   <si>
     <t>€ 4.228,92</t>
@@ -1234,10 +1234,10 @@
     <t>€ 492,73</t>
   </si>
   <si>
-    <t>€ 1.117,64</t>
-  </si>
-  <si>
-    <t>€ 20.991,72</t>
+    <t>€ 1.718,17</t>
+  </si>
+  <si>
+    <t>€ 32.301,64</t>
   </si>
   <si>
     <t>€ 5.498,72</t>
@@ -1270,7 +1270,7 @@
     <t>€ 1.045,15</t>
   </si>
   <si>
-    <t>€ 650,27</t>
+    <t>€ 1.000,04</t>
   </si>
   <si>
     <t>€ 11.040,68</t>
@@ -1285,7 +1285,7 @@
     <t>€ 7.905,69</t>
   </si>
   <si>
-    <t>€ 739,25</t>
+    <t>€ 854,68</t>
   </si>
   <si>
     <t>€ 451,10</t>
@@ -1309,7 +1309,7 @@
     <t>€ -70,03</t>
   </si>
   <si>
-    <t>€ 3.796,58</t>
+    <t>€ 5.840,89</t>
   </si>
   <si>
     <t>€ 681,67</t>
@@ -1324,7 +1324,7 @@
     <t>€ 9.898,53</t>
   </si>
   <si>
-    <t>€ 1.018,62</t>
+    <t>€ 1.565,50</t>
   </si>
   <si>
     <t>€ -78,82</t>
@@ -1763,7 +1763,7 @@
         <v>42</v>
       </c>
       <c r="D4">
-        <v>1532</v>
+        <v>2357</v>
       </c>
       <c r="E4" t="s">
         <v>48</v>
@@ -1797,7 +1797,7 @@
         <v>42</v>
       </c>
       <c r="D6">
-        <v>324</v>
+        <v>373</v>
       </c>
       <c r="E6" t="s">
         <v>50</v>
@@ -1899,7 +1899,7 @@
         <v>43</v>
       </c>
       <c r="D12">
-        <v>333</v>
+        <v>384</v>
       </c>
       <c r="E12" t="s">
         <v>56</v>
@@ -1916,7 +1916,7 @@
         <v>43</v>
       </c>
       <c r="D13">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="E13" t="s">
         <v>57</v>
@@ -1933,7 +1933,7 @@
         <v>44</v>
       </c>
       <c r="D14">
-        <v>333</v>
+        <v>384</v>
       </c>
       <c r="E14" t="s">
         <v>58</v>
@@ -1984,7 +1984,7 @@
         <v>43</v>
       </c>
       <c r="D17">
-        <v>871</v>
+        <v>1340</v>
       </c>
       <c r="E17" t="s">
         <v>61</v>
@@ -2035,7 +2035,7 @@
         <v>42</v>
       </c>
       <c r="D20">
-        <v>884</v>
+        <v>1020</v>
       </c>
       <c r="E20" t="s">
         <v>63</v>
@@ -2069,7 +2069,7 @@
         <v>43</v>
       </c>
       <c r="D22">
-        <v>230</v>
+        <v>355</v>
       </c>
       <c r="E22" t="s">
         <v>65</v>
@@ -2222,7 +2222,7 @@
         <v>43</v>
       </c>
       <c r="D31">
-        <v>393</v>
+        <v>605</v>
       </c>
       <c r="E31" t="s">
         <v>74</v>
@@ -2460,7 +2460,7 @@
         <v>44</v>
       </c>
       <c r="D45">
-        <v>262</v>
+        <v>403</v>
       </c>
       <c r="E45" t="s">
         <v>88</v>
@@ -2494,7 +2494,7 @@
         <v>44</v>
       </c>
       <c r="D47">
-        <v>1155</v>
+        <v>1777</v>
       </c>
       <c r="E47" t="s">
         <v>90</v>
@@ -2613,7 +2613,7 @@
         <v>43</v>
       </c>
       <c r="D54">
-        <v>1036</v>
+        <v>1593</v>
       </c>
       <c r="E54" t="s">
         <v>96</v>
@@ -2630,7 +2630,7 @@
         <v>43</v>
       </c>
       <c r="D55">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="E55" t="s">
         <v>57</v>
@@ -2851,7 +2851,7 @@
         <v>45</v>
       </c>
       <c r="D68">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="E68" t="s">
         <v>108</v>
@@ -2970,7 +2970,7 @@
         <v>44</v>
       </c>
       <c r="D75">
-        <v>1107</v>
+        <v>1277</v>
       </c>
       <c r="E75" t="s">
         <v>115</v>
@@ -2987,7 +2987,7 @@
         <v>42</v>
       </c>
       <c r="D76">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="E76" t="s">
         <v>116</v>
@@ -3106,7 +3106,7 @@
         <v>43</v>
       </c>
       <c r="D83">
-        <v>632</v>
+        <v>729</v>
       </c>
       <c r="E83" t="s">
         <v>123</v>
@@ -3276,7 +3276,7 @@
         <v>42</v>
       </c>
       <c r="D93">
-        <v>340</v>
+        <v>393</v>
       </c>
       <c r="E93" t="s">
         <v>133</v>
@@ -3650,7 +3650,7 @@
         <v>42</v>
       </c>
       <c r="D115">
-        <v>251</v>
+        <v>386</v>
       </c>
       <c r="E115" t="s">
         <v>155</v>
@@ -3667,7 +3667,7 @@
         <v>44</v>
       </c>
       <c r="D116">
-        <v>343</v>
+        <v>396</v>
       </c>
       <c r="E116" t="s">
         <v>156</v>
@@ -3718,7 +3718,7 @@
         <v>45</v>
       </c>
       <c r="D119">
-        <v>253</v>
+        <v>292</v>
       </c>
       <c r="E119" t="s">
         <v>159</v>
@@ -3905,7 +3905,7 @@
         <v>42</v>
       </c>
       <c r="D130">
-        <v>329</v>
+        <v>380</v>
       </c>
       <c r="E130" t="s">
         <v>169</v>
@@ -3922,7 +3922,7 @@
         <v>45</v>
       </c>
       <c r="D131">
-        <v>974</v>
+        <v>1499</v>
       </c>
       <c r="E131" t="s">
         <v>170</v>
@@ -3973,7 +3973,7 @@
         <v>44</v>
       </c>
       <c r="D134">
-        <v>396</v>
+        <v>457</v>
       </c>
       <c r="E134" t="s">
         <v>173</v>
@@ -3990,7 +3990,7 @@
         <v>42</v>
       </c>
       <c r="D135">
-        <v>976</v>
+        <v>1502</v>
       </c>
       <c r="E135" t="s">
         <v>174</v>
@@ -4228,7 +4228,7 @@
         <v>45</v>
       </c>
       <c r="D149">
-        <v>439</v>
+        <v>507</v>
       </c>
       <c r="E149" t="s">
         <v>188</v>
@@ -4262,7 +4262,7 @@
         <v>43</v>
       </c>
       <c r="D151">
-        <v>512</v>
+        <v>591</v>
       </c>
       <c r="E151" t="s">
         <v>190</v>
@@ -4279,7 +4279,7 @@
         <v>43</v>
       </c>
       <c r="D152">
-        <v>300</v>
+        <v>347</v>
       </c>
       <c r="E152" t="s">
         <v>191</v>
@@ -4330,7 +4330,7 @@
         <v>45</v>
       </c>
       <c r="D155">
-        <v>987</v>
+        <v>1519</v>
       </c>
       <c r="E155" t="s">
         <v>194</v>
@@ -4347,7 +4347,7 @@
         <v>45</v>
       </c>
       <c r="D156">
-        <v>331</v>
+        <v>510</v>
       </c>
       <c r="E156" t="s">
         <v>195</v>
@@ -4398,7 +4398,7 @@
         <v>42</v>
       </c>
       <c r="D159">
-        <v>276</v>
+        <v>425</v>
       </c>
       <c r="E159" t="s">
         <v>198</v>
@@ -4415,7 +4415,7 @@
         <v>42</v>
       </c>
       <c r="D160">
-        <v>492</v>
+        <v>757</v>
       </c>
       <c r="E160" t="s">
         <v>199</v>
@@ -4432,7 +4432,7 @@
         <v>44</v>
       </c>
       <c r="D161">
-        <v>548</v>
+        <v>632</v>
       </c>
       <c r="E161" t="s">
         <v>200</v>
@@ -4568,7 +4568,7 @@
         <v>45</v>
       </c>
       <c r="D169">
-        <v>1844</v>
+        <v>2838</v>
       </c>
       <c r="E169" t="s">
         <v>208</v>
@@ -4653,7 +4653,7 @@
         <v>43</v>
       </c>
       <c r="D174">
-        <v>663</v>
+        <v>765</v>
       </c>
       <c r="E174" t="s">
         <v>213</v>
@@ -4840,7 +4840,7 @@
         <v>44</v>
       </c>
       <c r="D185">
-        <v>-57</v>
+        <v>-87</v>
       </c>
       <c r="E185" t="s">
         <v>224</v>
@@ -4908,7 +4908,7 @@
         <v>44</v>
       </c>
       <c r="D189">
-        <v>448</v>
+        <v>517</v>
       </c>
       <c r="E189" t="s">
         <v>91</v>
@@ -4959,7 +4959,7 @@
         <v>45</v>
       </c>
       <c r="D192">
-        <v>831</v>
+        <v>1278</v>
       </c>
       <c r="E192" t="s">
         <v>229</v>
@@ -5027,7 +5027,7 @@
         <v>43</v>
       </c>
       <c r="D196">
-        <v>230</v>
+        <v>355</v>
       </c>
       <c r="E196" t="s">
         <v>65</v>
@@ -5197,7 +5197,7 @@
         <v>43</v>
       </c>
       <c r="D206">
-        <v>381</v>
+        <v>440</v>
       </c>
       <c r="E206" t="s">
         <v>242</v>
@@ -5384,7 +5384,7 @@
         <v>44</v>
       </c>
       <c r="D217">
-        <v>399</v>
+        <v>613</v>
       </c>
       <c r="E217" t="s">
         <v>253</v>
@@ -5418,7 +5418,7 @@
         <v>42</v>
       </c>
       <c r="D219">
-        <v>2013</v>
+        <v>3097</v>
       </c>
       <c r="E219" t="s">
         <v>255</v>
@@ -5435,7 +5435,7 @@
         <v>43</v>
       </c>
       <c r="D220">
-        <v>339</v>
+        <v>522</v>
       </c>
       <c r="E220" t="s">
         <v>256</v>
@@ -5571,7 +5571,7 @@
         <v>42</v>
       </c>
       <c r="D228">
-        <v>619</v>
+        <v>952</v>
       </c>
       <c r="E228" t="s">
         <v>264</v>
@@ -5758,7 +5758,7 @@
         <v>44</v>
       </c>
       <c r="D239">
-        <v>-34</v>
+        <v>-39</v>
       </c>
       <c r="E239" t="s">
         <v>275</v>
@@ -6047,7 +6047,7 @@
         <v>43</v>
       </c>
       <c r="D256">
-        <v>258</v>
+        <v>397</v>
       </c>
       <c r="E256" t="s">
         <v>292</v>
@@ -6149,7 +6149,7 @@
         <v>45</v>
       </c>
       <c r="D262">
-        <v>515</v>
+        <v>594</v>
       </c>
       <c r="E262" t="s">
         <v>298</v>
@@ -6268,7 +6268,7 @@
         <v>45</v>
       </c>
       <c r="D269">
-        <v>154</v>
+        <v>236</v>
       </c>
       <c r="E269" t="s">
         <v>305</v>
@@ -6302,7 +6302,7 @@
         <v>43</v>
       </c>
       <c r="D271">
-        <v>381</v>
+        <v>440</v>
       </c>
       <c r="E271" t="s">
         <v>242</v>
@@ -6387,7 +6387,7 @@
         <v>43</v>
       </c>
       <c r="D276">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="E276" t="s">
         <v>310</v>
@@ -6438,7 +6438,7 @@
         <v>42</v>
       </c>
       <c r="D279">
-        <v>781</v>
+        <v>1202</v>
       </c>
       <c r="E279" t="s">
         <v>313</v>
@@ -6489,7 +6489,7 @@
         <v>45</v>
       </c>
       <c r="D282">
-        <v>252</v>
+        <v>291</v>
       </c>
       <c r="E282" t="s">
         <v>316</v>
@@ -6574,7 +6574,7 @@
         <v>43</v>
       </c>
       <c r="D287">
-        <v>1586</v>
+        <v>2440</v>
       </c>
       <c r="E287" t="s">
         <v>320</v>
@@ -6591,7 +6591,7 @@
         <v>45</v>
       </c>
       <c r="D288">
-        <v>343</v>
+        <v>396</v>
       </c>
       <c r="E288" t="s">
         <v>321</v>
@@ -6608,7 +6608,7 @@
         <v>42</v>
       </c>
       <c r="D289">
-        <v>391</v>
+        <v>601</v>
       </c>
       <c r="E289" t="s">
         <v>322</v>
@@ -6659,7 +6659,7 @@
         <v>42</v>
       </c>
       <c r="D292">
-        <v>916</v>
+        <v>1057</v>
       </c>
       <c r="E292" t="s">
         <v>325</v>
@@ -6829,7 +6829,7 @@
         <v>42</v>
       </c>
       <c r="D302">
-        <v>774</v>
+        <v>893</v>
       </c>
       <c r="E302" t="s">
         <v>335</v>
@@ -6914,7 +6914,7 @@
         <v>42</v>
       </c>
       <c r="D307">
-        <v>619</v>
+        <v>952</v>
       </c>
       <c r="E307" t="s">
         <v>264</v>
@@ -6931,7 +6931,7 @@
         <v>45</v>
       </c>
       <c r="D308">
-        <v>689</v>
+        <v>795</v>
       </c>
       <c r="E308" t="s">
         <v>340</v>
@@ -7101,7 +7101,7 @@
         <v>44</v>
       </c>
       <c r="D318">
-        <v>802</v>
+        <v>926</v>
       </c>
       <c r="E318" t="s">
         <v>349</v>
@@ -7135,7 +7135,7 @@
         <v>42</v>
       </c>
       <c r="D320">
-        <v>558</v>
+        <v>644</v>
       </c>
       <c r="E320" t="s">
         <v>351</v>
@@ -7152,7 +7152,7 @@
         <v>44</v>
       </c>
       <c r="D321">
-        <v>500</v>
+        <v>577</v>
       </c>
       <c r="E321" t="s">
         <v>352</v>
@@ -7322,7 +7322,7 @@
         <v>45</v>
       </c>
       <c r="D331">
-        <v>899</v>
+        <v>1384</v>
       </c>
       <c r="E331" t="s">
         <v>361</v>
@@ -7339,7 +7339,7 @@
         <v>42</v>
       </c>
       <c r="D332">
-        <v>858</v>
+        <v>990</v>
       </c>
       <c r="E332" t="s">
         <v>362</v>
@@ -7475,7 +7475,7 @@
         <v>43</v>
       </c>
       <c r="D340">
-        <v>644</v>
+        <v>743</v>
       </c>
       <c r="E340" t="s">
         <v>370</v>
@@ -7611,7 +7611,7 @@
         <v>43</v>
       </c>
       <c r="D348">
-        <v>393</v>
+        <v>605</v>
       </c>
       <c r="E348" t="s">
         <v>74</v>
@@ -7968,7 +7968,7 @@
         <v>42</v>
       </c>
       <c r="D369">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="E369" t="s">
         <v>396</v>
@@ -8138,7 +8138,7 @@
         <v>44</v>
       </c>
       <c r="D379">
-        <v>603</v>
+        <v>927</v>
       </c>
       <c r="E379" t="s">
         <v>406</v>
@@ -8155,7 +8155,7 @@
         <v>42</v>
       </c>
       <c r="D380">
-        <v>967</v>
+        <v>1488</v>
       </c>
       <c r="E380" t="s">
         <v>407</v>
@@ -8342,7 +8342,7 @@
         <v>45</v>
       </c>
       <c r="D391">
-        <v>264</v>
+        <v>406</v>
       </c>
       <c r="E391" t="s">
         <v>418</v>
@@ -8427,7 +8427,7 @@
         <v>45</v>
       </c>
       <c r="D396">
-        <v>301</v>
+        <v>348</v>
       </c>
       <c r="E396" t="s">
         <v>423</v>
@@ -8580,7 +8580,7 @@
         <v>43</v>
       </c>
       <c r="D405">
-        <v>403</v>
+        <v>620</v>
       </c>
       <c r="E405" t="s">
         <v>431</v>
@@ -8665,7 +8665,7 @@
         <v>44</v>
       </c>
       <c r="D410">
-        <v>583</v>
+        <v>896</v>
       </c>
       <c r="E410" t="s">
         <v>436</v>
